--- a/diseases/d029/2005-2009.xlsx
+++ b/diseases/d029/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2140,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2681,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2989,9 +2974,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3533,9 +3515,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3829,9 +3808,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4373,9 +4349,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4669,9 +4642,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5213,9 +5183,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5509,9 +5476,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6053,9 +6017,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6349,9 +6310,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6893,9 +6851,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7189,9 +7144,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7733,9 +7685,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8029,9 +7978,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8573,9 +8519,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8869,9 +8812,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9413,9 +9353,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9709,9 +9646,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10253,9 +10187,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10549,9 +10480,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11093,9 +11021,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11389,9 +11314,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11933,9 +11855,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12329,9 +12248,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12625,9 +12541,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13169,9 +13082,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13465,9 +13375,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14009,9 +13916,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14305,9 +14209,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14849,9 +14750,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15145,9 +15043,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15689,9 +15584,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15985,9 +15877,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16529,9 +16418,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -16825,9 +16711,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17369,9 +17252,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17665,9 +17545,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18209,9 +18086,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18505,9 +18379,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19049,9 +18920,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19345,9 +19213,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19889,9 +19754,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20185,9 +20047,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20729,9 +20588,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21025,9 +20881,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21569,9 +21422,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22013,9 +21863,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22557,9 +22404,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22953,9 +22797,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23397,9 +23238,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -23941,9 +23779,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24385,9 +24220,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24929,9 +24761,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -25373,9 +25202,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -25917,9 +25743,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -26361,9 +26184,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26905,9 +26725,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -27349,9 +27166,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -27893,9 +27707,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -28337,9 +28148,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28881,9 +28689,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -29325,9 +29130,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -29869,9 +29671,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -30313,9 +30112,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -30857,9 +30653,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -31301,9 +31094,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -31845,9 +31635,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -32289,9 +32076,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32833,9 +32617,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -33277,9 +33058,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -33821,9 +33599,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -34117,9 +33892,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -34661,9 +34433,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -35057,9 +34826,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -35205,9 +34971,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -35749,9 +35512,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -36293,9 +36053,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -36441,9 +36198,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -36985,9 +36739,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -37529,9 +37280,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -37677,9 +37425,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -38221,9 +37966,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -38765,9 +38507,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -38913,9 +38652,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -39457,9 +39193,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -40001,9 +39734,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -40149,9 +39879,6 @@
       <c r="O235" t="n">
         <v>4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -40693,9 +40420,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -41237,9 +40961,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -41385,9 +41106,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -41929,9 +41647,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -42473,9 +42188,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -42621,9 +42333,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -43165,9 +42874,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -43709,9 +43415,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -43857,9 +43560,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -44401,9 +44101,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -44945,9 +44642,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -45093,9 +44787,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -45637,9 +45328,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -46181,9 +45869,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -46329,9 +46014,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -46873,9 +46555,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -47417,9 +47096,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -47565,9 +47241,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -48109,9 +47782,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -48653,9 +48323,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -48801,9 +48468,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -49493,9 +49157,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -50037,9 +49698,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -50433,9 +50091,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -50877,9 +50532,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -51421,9 +51073,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -51865,9 +51514,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -52409,9 +52055,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -52853,9 +52496,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -53397,9 +53037,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -53841,9 +53478,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -54385,9 +54019,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -54829,9 +54460,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -55373,9 +55001,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -55817,9 +55442,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -56361,9 +55983,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -56805,9 +56424,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -57349,9 +56965,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -57793,9 +57406,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -58337,9 +57947,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -58781,9 +58388,6 @@
       <c r="O344" t="n">
         <v>0</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0</v>
       </c>
@@ -59325,9 +58929,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -59769,9 +59370,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -60313,9 +59911,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -60757,9 +60352,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -61299,9 +60891,6 @@
         <v>0</v>
       </c>
       <c r="O359" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q359" t="n">
         <v>0</v>
       </c>
       <c r="R359" t="n">
